--- a/Austerlitz/Turns/136HJan1808a.xlsx
+++ b/Austerlitz/Turns/136HJan1808a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Austerlitz\Austerlitz\Turns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7643EB3A-132E-45FE-9B0E-FCCAE1CDBA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D554F-19DD-4F14-AA3A-8B4E2245CCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7671,7 +7671,7 @@
         <v>4156</v>
       </c>
       <c r="C215" s="11">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D215" s="11">
         <v>1</v>

--- a/Austerlitz/Turns/136HJan1808a.xlsx
+++ b/Austerlitz/Turns/136HJan1808a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Austerlitz\Austerlitz\Turns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D554F-19DD-4F14-AA3A-8B4E2245CCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43B9363-2FDB-4F9D-920B-1C409B67979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
   <si>
     <t>A U S T E R L I T Z</t>
   </si>
@@ -242,15 +242,6 @@
     <t>(23) Change State Relationships  (State/New Relationship)</t>
   </si>
   <si>
-    <t>4156</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -267,9 +258,6 @@
   </si>
   <si>
     <t>Kt Muskets</t>
-  </si>
-  <si>
-    <t>Colonial Musket</t>
   </si>
 </sst>
 </file>
@@ -541,7 +529,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF4C7C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -762,7 +758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L308"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.59765625" customWidth="1"/>
     <col min="2" max="6" width="7.09765625" customWidth="1"/>
@@ -841,7 +837,7 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="5" t="s">
@@ -871,7 +867,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H6" s="29"/>
       <c r="I6" s="30"/>
@@ -889,7 +885,7 @@
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H7" s="29"/>
       <c r="I7" s="30"/>
@@ -975,21 +971,11 @@
       <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="11">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11">
-        <v>206</v>
-      </c>
-      <c r="D12" s="12">
-        <v>5456000</v>
-      </c>
-      <c r="E12" s="11">
-        <v>32000</v>
-      </c>
-      <c r="F12" s="11">
-        <v>6016</v>
-      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -1038,25 +1024,35 @@
       )
     )
   )))</f>
-        <v>Valid</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:12" ht="13.5" customHeight="1">
       <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="11">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11">
+        <v>206</v>
+      </c>
+      <c r="D13" s="11">
+        <v>4720000</v>
+      </c>
+      <c r="E13" s="11">
+        <v>32000</v>
+      </c>
+      <c r="F13" s="11">
+        <v>7488</v>
+      </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Valid</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.5" customHeight="1">
@@ -1251,11 +1247,11 @@
       <c r="A25" s="5">
         <v>1</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>70</v>
+      <c r="B25" s="14">
+        <v>4156</v>
+      </c>
+      <c r="C25" s="14">
+        <v>2</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1307,11 +1303,11 @@
       <c r="A26" s="5">
         <v>2</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>71</v>
+      <c r="B26" s="15">
+        <v>4156</v>
+      </c>
+      <c r="C26" s="14">
+        <v>3</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1467,24 +1463,24 @@
         <v>206</v>
       </c>
       <c r="C34" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E34" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F34" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G34" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="6" t="str">
@@ -1516,24 +1512,24 @@
         <v>206</v>
       </c>
       <c r="C35" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E35" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F35" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G35" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="6" t="str">
@@ -1549,24 +1545,24 @@
         <v>206</v>
       </c>
       <c r="C36" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F36" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G36" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="6" t="str">
@@ -1582,24 +1578,24 @@
         <v>206</v>
       </c>
       <c r="C37" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F37" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="str">
@@ -1615,24 +1611,24 @@
         <v>206</v>
       </c>
       <c r="C38" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F38" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G38" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="6" t="str">
@@ -1648,24 +1644,24 @@
         <v>206</v>
       </c>
       <c r="C39" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="11">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F39" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="6" t="str">
@@ -1698,7 +1694,7 @@
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
       <c r="J40" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="6" t="str">
@@ -1731,7 +1727,7 @@
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
       <c r="J41" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="6" t="str">
@@ -7682,12 +7678,8 @@
       <c r="F215" s="11">
         <v>3</v>
       </c>
-      <c r="G215" s="11">
-        <v>4</v>
-      </c>
-      <c r="H215" s="11">
-        <v>1</v>
-      </c>
+      <c r="G215" s="11"/>
+      <c r="H215" s="11"/>
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
       <c r="K215" s="6"/>
@@ -7834,12 +7826,8 @@
       <c r="F217" s="11">
         <v>3</v>
       </c>
-      <c r="G217" s="11">
-        <v>4</v>
-      </c>
-      <c r="H217" s="11">
-        <v>1</v>
-      </c>
+      <c r="G217" s="11"/>
+      <c r="H217" s="11"/>
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
       <c r="K217" s="6"/>
@@ -11168,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="B269" s="22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C269" s="16">
         <v>4153</v>
@@ -11245,7 +11233,7 @@
         <v>2</v>
       </c>
       <c r="B270" s="22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C270" s="11">
         <v>4176</v>
@@ -11322,7 +11310,7 @@
         <v>3</v>
       </c>
       <c r="B271" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C271" s="11">
         <v>3</v>
@@ -11399,7 +11387,7 @@
         <v>4</v>
       </c>
       <c r="B272" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C272" s="11">
         <v>95</v>
@@ -11476,7 +11464,7 @@
         <v>5</v>
       </c>
       <c r="B273" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C273" s="11">
         <v>2</v>
@@ -11553,7 +11541,7 @@
         <v>6</v>
       </c>
       <c r="B274" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C274" s="11">
         <v>91</v>
@@ -13063,16 +13051,16 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G6:I6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12:I21 B25:C30 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B215:H244 B269:E284 B288:C293 B297:H300 B304:C307 B34:J41 B194:E211 B248:E265">
+  <conditionalFormatting sqref="B12:I21 B25:C30 B34:J41 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B194:E211 B215:H244 B248:E265 B269:E284 B288:C293 B297:H300 B304:C307">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($L12 &lt;&gt; "Valid",$L12&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C188:G190 B288:B293 B304:B307" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C188:G190 B288:B293 B304:B307" xr:uid="{4ABD8F44-469B-478E-8C13-B62A01BAED5F}">
       <formula1>"-,A,B,D,E,F,G,H,I,K,M,N,P,R,S,T,W"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{F6266FA2-2807-4FEC-946F-27DF73ABAA9E}">
       <formula1>"Choose,A,B,D,E,F,G,H,I,K,M,N,P,R,S,T,W"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Austerlitz/Turns/136HJan1808a.xlsx
+++ b/Austerlitz/Turns/136HJan1808a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Austerlitz\Austerlitz\Turns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43B9363-2FDB-4F9D-920B-1C409B67979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B252632-842A-431E-9A67-59B3760B06D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="1530" windowWidth="18060" windowHeight="20070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5160,12 +5160,8 @@
       <c r="A166" s="5">
         <v>11</v>
       </c>
-      <c r="B166" s="16">
-        <v>4</v>
-      </c>
-      <c r="C166" s="11">
-        <v>61</v>
-      </c>
+      <c r="B166" s="16"/>
+      <c r="C166" s="11"/>
       <c r="D166" s="5"/>
       <c r="E166" s="21"/>
       <c r="F166" s="21"/>
@@ -5222,12 +5218,8 @@
       <c r="A167" s="5">
         <v>12</v>
       </c>
-      <c r="B167" s="11">
-        <v>4211</v>
-      </c>
-      <c r="C167" s="16">
-        <v>61</v>
-      </c>
+      <c r="B167" s="11"/>
+      <c r="C167" s="16"/>
       <c r="D167" s="5"/>
       <c r="E167" s="21"/>
       <c r="F167" s="21"/>
@@ -8111,13 +8103,27 @@
       <c r="A221" s="5">
         <v>7</v>
       </c>
-      <c r="B221" s="11"/>
-      <c r="C221" s="11"/>
-      <c r="D221" s="11"/>
-      <c r="E221" s="11"/>
-      <c r="F221" s="11"/>
-      <c r="G221" s="11"/>
-      <c r="H221" s="11"/>
+      <c r="B221" s="11">
+        <v>1401</v>
+      </c>
+      <c r="C221" s="11">
+        <v>1</v>
+      </c>
+      <c r="D221" s="11">
+        <v>2</v>
+      </c>
+      <c r="E221" s="11">
+        <v>2</v>
+      </c>
+      <c r="F221" s="11">
+        <v>2</v>
+      </c>
+      <c r="G221" s="11">
+        <v>4</v>
+      </c>
+      <c r="H221" s="11">
+        <v>3</v>
+      </c>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="6"/>
@@ -8175,11 +8181,21 @@
       <c r="A222" s="5">
         <v>8</v>
       </c>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
-      <c r="D222" s="11"/>
-      <c r="E222" s="11"/>
-      <c r="F222" s="11"/>
+      <c r="B222" s="11">
+        <v>1403</v>
+      </c>
+      <c r="C222" s="11">
+        <v>1</v>
+      </c>
+      <c r="D222" s="11">
+        <v>1</v>
+      </c>
+      <c r="E222" s="11">
+        <v>5</v>
+      </c>
+      <c r="F222" s="11">
+        <v>1</v>
+      </c>
       <c r="G222" s="11"/>
       <c r="H222" s="11"/>
       <c r="I222" s="5"/>
@@ -8303,13 +8319,27 @@
       <c r="A224" s="5">
         <v>10</v>
       </c>
-      <c r="B224" s="11"/>
-      <c r="C224" s="16"/>
-      <c r="D224" s="11"/>
-      <c r="E224" s="16"/>
-      <c r="F224" s="16"/>
-      <c r="G224" s="16"/>
-      <c r="H224" s="16"/>
+      <c r="B224" s="11">
+        <v>7007</v>
+      </c>
+      <c r="C224" s="16">
+        <v>4</v>
+      </c>
+      <c r="D224" s="11">
+        <v>2</v>
+      </c>
+      <c r="E224" s="16">
+        <v>2</v>
+      </c>
+      <c r="F224" s="16">
+        <v>4</v>
+      </c>
+      <c r="G224" s="16">
+        <v>1</v>
+      </c>
+      <c r="H224" s="16">
+        <v>1</v>
+      </c>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="6"/>
@@ -13051,8 +13081,13 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G6:I6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12:I21 B25:C30 B34:J41 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B194:E211 B215:H244 B248:E265 B269:E284 B288:C293 B297:H300 B304:C307">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="B215:H244">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND($L215 &lt;&gt; "Valid",$L215&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:I21 B25:C30 B34:J41 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B194:E211 B248:E265 B269:E284 B288:C293 B297:H300 B304:C307">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND($L12 &lt;&gt; "Valid",$L12&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Austerlitz/Turns/136HJan1808a.xlsx
+++ b/Austerlitz/Turns/136HJan1808a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\Austerlitz\Austerlitz\Turns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B252632-842A-431E-9A67-59B3760B06D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070522E1-DC5C-4FC9-AE24-A206B9D7F39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="1530" windowWidth="18060" windowHeight="20070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27345" yWindow="2190" windowWidth="18060" windowHeight="20070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -529,7 +529,31 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF4C7C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF4C7C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FFF4C7C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1037,17 +1061,19 @@
       <c r="C13" s="11">
         <v>206</v>
       </c>
-      <c r="D13" s="11">
-        <v>4720000</v>
+      <c r="D13" s="12">
+        <v>5352000</v>
       </c>
       <c r="E13" s="11">
         <v>32000</v>
       </c>
       <c r="F13" s="11">
-        <v>7488</v>
+        <v>6624</v>
       </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="H13" s="11">
+        <v>5600</v>
+      </c>
       <c r="I13" s="11"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6" t="str">
@@ -1466,16 +1492,16 @@
         <v>1</v>
       </c>
       <c r="D34" s="11">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F34" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -1515,16 +1541,16 @@
         <v>1</v>
       </c>
       <c r="D35" s="11">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F35" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
@@ -1551,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F36" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G36" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
@@ -1584,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F37" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
@@ -1617,13 +1643,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F38" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G38" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
@@ -1650,13 +1676,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="11">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F39" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G39" s="11">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
@@ -1677,19 +1703,19 @@
         <v>206</v>
       </c>
       <c r="C40" s="11">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D40" s="11">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E40" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F40" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G40" s="11">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -1716,13 +1742,13 @@
         <v>19</v>
       </c>
       <c r="E41" s="11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F41" s="11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G41" s="11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -3702,8 +3728,12 @@
       <c r="A133" s="5">
         <v>1</v>
       </c>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
+      <c r="B133" s="11">
+        <v>76</v>
+      </c>
+      <c r="C133" s="11">
+        <v>96</v>
+      </c>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -4356,13 +4386,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C150" s="11">
         <v>29</v>
       </c>
       <c r="D150" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="21"/>
@@ -4403,13 +4433,13 @@
         <v>9</v>
       </c>
       <c r="B151" s="11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C151" s="11">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D151" s="11">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="21"/>
@@ -13081,14 +13111,29 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G6:I6"/>
   </mergeCells>
+  <conditionalFormatting sqref="B25:C30 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B194:E211 B248:E265 B269:E284 B288:C293 B297:H300 B304:C307">
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>AND($L25 &lt;&gt; "Valid",$L25&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B215:H244">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND($L215 &lt;&gt; "Valid",$L215&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:I21 B25:C30 B34:J41 B45:C50 B54:C65 B69:B84 B88:E91 B95:E102 B106:B111 B115:F122 B126:B129 B133:C139 B143:D152 B156:C176 B180:C184 B188:G190 B194:E211 B248:E265 B269:E284 B288:C293 B297:H300 B304:C307">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="B12:I12 B14:I21 I13">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND($L12 &lt;&gt; "Valid",$L12&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:H13">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($L13 &lt;&gt; "Valid",$L13&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:J41">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($L34 &lt;&gt; "Valid",$L34&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
